--- a/results/Int All Data -0.0/Rando_7_permute.xlsx
+++ b/results/Int All Data -0.0/Rando_7_permute.xlsx
@@ -440,27 +440,27 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7553686057617557</v>
+        <v>0.74166999844517</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7575764643166523</v>
+        <v>0.741640567735057</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7565608271695432</v>
+        <v>0.7392216965416138</v>
       </c>
     </row>
     <row r="5">
@@ -470,217 +470,217 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7565608271695432</v>
+        <v>0.7392216965416138</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7565608271695432</v>
+        <v>0.7435785522311811</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7554568978920948</v>
+        <v>0.7432203860420692</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7624925034983674</v>
+        <v>0.7442948846094045</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7624042113680283</v>
+        <v>0.7466204660047533</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7624042113680283</v>
+        <v>0.7414589858066236</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7635375713555896</v>
+        <v>0.7406837920081739</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7635375713555896</v>
+        <v>0.7402961951089492</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7621343373092557</v>
+        <v>0.7406837920081739</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7653872637213744</v>
+        <v>0.7402323360209679</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7648769463139424</v>
+        <v>0.7402323360209679</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7626690877590457</v>
+        <v>0.7404433486595144</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7549415828169077</v>
+        <v>0.7404139179494014</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7549415828169077</v>
+        <v>0.7443537460296306</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7525865707114459</v>
+        <v>0.7420281646342818</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7493042135892138</v>
+        <v>0.7390795406588037</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7496329490682125</v>
+        <v>0.737318140423358</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7360620599275893</v>
+        <v>0.7388440949778992</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.741164678705493</v>
+        <v>0.7461989960240776</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7398791674996112</v>
+        <v>0.7473323560116391</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7439661491304058</v>
+        <v>0.7471213433730926</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7490099064880833</v>
+        <v>0.7471213433730926</v>
       </c>
     </row>
     <row r="27">
@@ -690,1297 +690,1297 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7479354079207481</v>
+        <v>0.7467043157637547</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7475478110215232</v>
+        <v>0.7397470069523111</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7426856355922792</v>
+        <v>0.7366706648008707</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.760804957686413</v>
+        <v>0.7366706648008707</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7577924746229537</v>
+        <v>0.7304396837031607</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7626496523844428</v>
+        <v>0.7335698896070723</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7624680704560094</v>
+        <v>0.7335698896070723</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7621099042668977</v>
+        <v>0.7183703160747207</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7521351147242398</v>
+        <v>0.7119333200062192</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7535677794806868</v>
+        <v>0.7079396281735191</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.758493813997912</v>
+        <v>0.7085970991315164</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7533617645098953</v>
+        <v>0.7121149019346527</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.752198973812221</v>
+        <v>0.7200728548899402</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7525571400013327</v>
+        <v>0.7170309411163679</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7522334021900891</v>
+        <v>0.7114868616867684</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7459041336265299</v>
+        <v>0.7372787143777348</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7422586126474312</v>
+        <v>0.7310083072344018</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7360176362142111</v>
+        <v>0.7178688834099642</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7360470669243242</v>
+        <v>0.7156315941449546</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7289964683147865</v>
+        <v>0.7103573887741277</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7152734279558428</v>
+        <v>0.7125652473290243</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7084094089424935</v>
+        <v>0.7068934497234624</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7155383043468604</v>
+        <v>0.701913551453766</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.709631061060394</v>
+        <v>0.7045384376180005</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.687552475511428</v>
+        <v>0.6996074054330201</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6905993869527554</v>
+        <v>0.7096949201483752</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.689490460007552</v>
+        <v>0.7092190311188111</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.689014570977988</v>
+        <v>0.6876263299349192</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.689014570977988</v>
+        <v>0.6888774127629329</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6886858354989893</v>
+        <v>0.6879550654139179</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6670537082694743</v>
+        <v>0.6875674685146932</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6552342240287866</v>
+        <v>0.6623436840585505</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6613524799537993</v>
+        <v>0.6653855978321228</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6613524799537993</v>
+        <v>0.664998000932898</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6522511716754403</v>
+        <v>0.6534972568356989</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6119744119410941</v>
+        <v>0.6482230514648719</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6115868150418693</v>
+        <v>0.6482230514648719</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.627728726594256</v>
+        <v>0.6513876857466516</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6264337753492815</v>
+        <v>0.656402012394216</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.615178472268497</v>
+        <v>0.6733585437906755</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.603771017969392</v>
+        <v>0.6990776526509851</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6044873503476156</v>
+        <v>0.7076047844339308</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5961906665778192</v>
+        <v>0.7076047844339308</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5957442082583684</v>
+        <v>0.7140123497923192</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5972063037249284</v>
+        <v>0.710548410741654</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.589866395682015</v>
+        <v>0.710548410741654</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5814714244463695</v>
+        <v>0.7058578219053331</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5843711823371316</v>
+        <v>0.7239182825792407</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5903667177539371</v>
+        <v>0.7234768219275449</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5955970547078031</v>
+        <v>0.7231186557384333</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5934774882832456</v>
+        <v>0.7219314319984007</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5981925101619244</v>
+        <v>0.7110048643966149</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5981925101619244</v>
+        <v>0.7144982341573932</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5798177517158659</v>
+        <v>0.7066674440816507</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5809511117034273</v>
+        <v>0.697678860975989</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5685380155927234</v>
+        <v>0.6977377223962151</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.571751515959219</v>
+        <v>0.6946075164923036</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.57219797427867</v>
+        <v>0.6949656826814153</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5717465182914639</v>
+        <v>0.6949656826814153</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5756030519091091</v>
+        <v>0.6876063392638991</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5792091468425846</v>
+        <v>0.6910852713178295</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5799254792208081</v>
+        <v>0.6919437595788632</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5509190155705116</v>
+        <v>0.6880039314986339</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5598437395881921</v>
+        <v>0.6700661913329335</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.5521606583594323</v>
+        <v>0.6792802247839896</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.568288132204971</v>
+        <v>0.6778475600275427</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5687051598143088</v>
+        <v>0.6910164145620933</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5673119211034851</v>
+        <v>0.6825331511961085</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5669537549143733</v>
+        <v>0.6849814530996646</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5669537549143733</v>
+        <v>0.6775188245485441</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5703588325448125</v>
+        <v>0.6781468647964284</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5700300970658138</v>
+        <v>0.6829946025188245</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5377662646320606</v>
+        <v>0.6858305013216055</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5412546367250839</v>
+        <v>0.6900696341707203</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5463816885453455</v>
+        <v>0.6897997601119478</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5671308944714689</v>
+        <v>0.6897997601119478</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5674301992403545</v>
+        <v>0.6873514582083917</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5705654028120211</v>
+        <v>0.6915905910575064</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5722679416272406</v>
+        <v>0.6847315697119123</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.552833677617112</v>
+        <v>0.6827641545056752</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5315352835343506</v>
+        <v>0.6632515937007174</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5350780746762622</v>
+        <v>0.6597237955620711</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5092956620243887</v>
+        <v>0.6698063126096711</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.4540991981519735</v>
+        <v>0.6824304213589214</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.4751765842606784</v>
+        <v>0.6831761844472579</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.4751765842606784</v>
+        <v>0.6916444548099776</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.4689111747851002</v>
+        <v>0.6890489993558562</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.4184691588369872</v>
+        <v>0.691733302236734</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.39924090979765</v>
+        <v>0.6831717420759201</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.39924090979765</v>
+        <v>0.6806940094622509</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.3692737833455498</v>
+        <v>0.6477732613669176</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.3729731680771196</v>
+        <v>0.6619477577130672</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4220846938095555</v>
+        <v>0.6412857333244486</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.4321672108571555</v>
+        <v>0.6469969569756336</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4476222207414318</v>
+        <v>0.6454171386686214</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.4650335399036006</v>
+        <v>0.6516581151018414</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4650335399036006</v>
+        <v>0.6463839097310144</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.4706953421736523</v>
+        <v>0.6463839097310144</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.4591457319917372</v>
+        <v>0.6520801403789342</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4625802403322893</v>
+        <v>0.6300354279114191</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4625802403322893</v>
+        <v>0.6300354279114191</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4625802403322893</v>
+        <v>0.5885364607627551</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4625802403322893</v>
+        <v>0.5719186601808045</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4441327380555741</v>
+        <v>0.5712856222651652</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4642189200595278</v>
+        <v>0.5735523422402879</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4642189200595278</v>
+        <v>0.5668893405299749</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4636841696097376</v>
+        <v>0.5707358788121099</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.4603918171519958</v>
+        <v>0.5553641633904178</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4603918171519958</v>
+        <v>0.5573315785966549</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4762438639745897</v>
+        <v>0.56265020768086</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4912374225361498</v>
+        <v>0.5640240110170809</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4986900557517603</v>
+        <v>0.564053441727194</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4999117078696608</v>
+        <v>0.5557417649541325</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5002698740587725</v>
+        <v>0.5643966149130406</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5017025388152195</v>
+        <v>0.5594267119788543</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5024483019035562</v>
+        <v>0.5534656049399169</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5017319695253326</v>
+        <v>0.5538482041713867</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5010450678572222</v>
+        <v>0.5549227027387219</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5017908309455588</v>
+        <v>0.5577586015415029</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5014032340463339</v>
+        <v>0.5290708780346949</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5014032340463339</v>
+        <v>0.5347226849692366</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5017614002354457</v>
+        <v>0.535856044956798</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5017614002354457</v>
+        <v>0.544962350902912</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5035228004708914</v>
+        <v>0.5688467604007019</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5035228004708914</v>
+        <v>0.5732919082206082</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.4969680815619377</v>
+        <v>0.5678555562959507</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4966982075031652</v>
+        <v>0.5678555562959507</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4990826503187401</v>
+        <v>0.5488499811199219</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5015848159747673</v>
+        <v>0.5615568290353391</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5015848159747673</v>
+        <v>0.498777237289265</v>
       </c>
     </row>
   </sheetData>
